--- a/app/reports/UFCS_research.xlsx
+++ b/app/reports/UFCS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-16 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-17 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>56.13</v>
+        <v>56.44</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.05105999946594238</v>
+        <v>0.05098000049591064</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>25705439.80046321</v>
+        <v>25705438.9794472</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>56.13</v>
+        <v>56.44</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>1442846336</v>
+        <v>1450814976</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>10.41</v>
+        <v>10.47</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>7.12</v>
+        <v>7.26</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>12913076224</v>
+        <v>12961784832</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>10.511014</v>
+        <v>10.550661</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>7.722</v>
+        <v>7.812</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.905</v>
+        <v>0.916</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>690232960</v>
+        <v>693388160</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>9.6848955</v>
+        <v>9.729167</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>7.339</v>
+        <v>7.408</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>0.698</v>
+        <v>0.704</v>
       </c>
     </row>
     <row r="8">
@@ -1580,16 +1580,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>8192032768</v>
+        <v>8319591424</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>14.589859</v>
+        <v>14.817039</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>11.14</v>
+        <v>11.381</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>4.087</v>
+        <v>4.175</v>
       </c>
     </row>
     <row r="9">
@@ -1604,16 +1604,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>302806112</v>
+        <v>302193984</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>39.05263</v>
+        <v>38.973686</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>21.194</v>
+        <v>21.109</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>0.945</v>
+        <v>0.9409999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1628,16 +1628,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>5539875328</v>
+        <v>5604575232</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>12.681723</v>
+        <v>12.829831</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>9.701000000000001</v>
+        <v>9.957000000000001</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>2.805</v>
+        <v>2.879</v>
       </c>
     </row>
     <row r="11">
@@ -1652,13 +1652,13 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>1527063680</v>
+        <v>1527210496</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>22.321888</v>
+        <v>22.324036</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>15.895</v>
+        <v>15.899</v>
       </c>
       <c r="F11" s="33" t="n">
         <v>1.181</v>
@@ -1676,16 +1676,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>5254592000</v>
+        <v>5311182848</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>10.810049</v>
+        <v>10.926472</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>8.271000000000001</v>
+        <v>8.426</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>1.082</v>
+        <v>1.103</v>
       </c>
     </row>
     <row r="13">
@@ -1700,16 +1700,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>2689761536</v>
+        <v>2718397184</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>14.056845</v>
+        <v>14.206496</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>8.433</v>
+        <v>8.590999999999999</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>1.441</v>
+        <v>1.467</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/UFCS_research.xlsx
+++ b/app/reports/UFCS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-17 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-18 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/UFCS_research.xlsx
+++ b/app/reports/UFCS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-18 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-19 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>56.44</v>
+        <v>56.22</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.05098000049591064</v>
+        <v>0.0514799976348877</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>25705438.9794472</v>
+        <v>25705439.48772679</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>56.44</v>
+        <v>56.22</v>
       </c>
     </row>
     <row r="38">
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>1450814976</v>
+        <v>1445159808</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>10.47</v>
+        <v>10.43</v>
       </c>
       <c r="E5" s="31" t="n">
         <v>7.26</v>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>693388160</v>
+        <v>686706688</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>9.729167</v>
+        <v>9.635417</v>
       </c>
       <c r="E7" s="33" t="n">
         <v>7.408</v>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>8319591424</v>
+        <v>8330753024</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>14.817039</v>
+        <v>14.836918</v>
       </c>
       <c r="E8" s="33" t="n">
         <v>11.381</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>302193984</v>
+        <v>301053344</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>38.973686</v>
+        <v>38.82658</v>
       </c>
       <c r="E9" s="33" t="n">
         <v>21.109</v>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>5604575232</v>
+        <v>5638531072</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>12.829831</v>
+        <v>12.907562</v>
       </c>
       <c r="E10" s="33" t="n">
         <v>9.957000000000001</v>
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>1527210496</v>
+        <v>1526770176</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>22.324036</v>
+        <v>22.317596</v>
       </c>
       <c r="E11" s="33" t="n">
         <v>15.899</v>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>5311182848</v>
+        <v>5308204544</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>10.926472</v>
+        <v>10.920343</v>
       </c>
       <c r="E12" s="33" t="n">
         <v>8.426</v>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>2718397184</v>
+        <v>2702858496</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>14.206496</v>
+        <v>14.125291</v>
       </c>
       <c r="E13" s="33" t="n">
         <v>8.590999999999999</v>

--- a/app/reports/UFCS_research.xlsx
+++ b/app/reports/UFCS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-19 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-20 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>56.22</v>
+        <v>56.61</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.0514799976348877</v>
+        <v>0.05126999855041504</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>25705439.48772679</v>
+        <v>25705441.15880587</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>56.22</v>
+        <v>56.61</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>1445159808</v>
+        <v>1455185024</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>10.43</v>
+        <v>10.5</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>7.26</v>
+        <v>7.21</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>12961784832</v>
+        <v>13002374144</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>10.550661</v>
+        <v>10.5837</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>7.812</v>
+        <v>7.802</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.916</v>
+        <v>0.915</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>686706688</v>
+        <v>693388160</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>9.635417</v>
+        <v>9.729167</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>7.408</v>
+        <v>7.298</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>0.704</v>
+        <v>0.694</v>
       </c>
     </row>
     <row r="8">
@@ -1580,16 +1580,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>8330753024</v>
+        <v>8447036416</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>14.836918</v>
+        <v>15.044016</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>11.381</v>
+        <v>11.392</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>4.175</v>
+        <v>4.179</v>
       </c>
     </row>
     <row r="9">
@@ -1604,16 +1604,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>301053344</v>
+        <v>301173728</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>38.82658</v>
+        <v>38.842106</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>21.109</v>
+        <v>21.006</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9370000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1628,16 +1628,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>5638531072</v>
+        <v>5722044416</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>12.907562</v>
+        <v>13.098739</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>9.957000000000001</v>
+        <v>10.763</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>2.879</v>
+        <v>2.889</v>
       </c>
     </row>
     <row r="11">
@@ -1652,16 +1652,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>1526770176</v>
+        <v>1527944576</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>22.317596</v>
+        <v>22.334764</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>15.899</v>
+        <v>15.872</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.181</v>
+        <v>1.179</v>
       </c>
     </row>
     <row r="12">
@@ -1676,16 +1676,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>5308204544</v>
+        <v>5323692544</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>10.920343</v>
+        <v>11.088089</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>8.426</v>
+        <v>8.401</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>1.103</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="13">
@@ -1700,16 +1700,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>2702858496</v>
+        <v>2722392832</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>14.125291</v>
+        <v>14.227378</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>8.590999999999999</v>
+        <v>8.499000000000001</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>1.467</v>
+        <v>1.452</v>
       </c>
     </row>
     <row r="15">
